--- a/output/pdf_financials_xlsx/CAT.xlsx
+++ b/output/pdf_financials_xlsx/CAT.xlsx
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>0.001896</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>0.003147</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.001917</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -3674,7 +3674,11 @@
           <t>Amortization included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n">
         <v>0.001896</v>
       </c>

--- a/output/pdf_financials_xlsx/CAT.xlsx
+++ b/output/pdf_financials_xlsx/CAT.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAT.xlsx
+++ b/output/pdf_financials_xlsx/CAT.xlsx
@@ -1899,20 +1899,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0.6832819999999999</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.633823</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.650267</v>
       </c>
     </row>
     <row r="65">
@@ -1975,25 +1969,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.082416</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.110916</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.118914</v>
       </c>
     </row>
     <row r="68">
